--- a/data/trans_camb/P32-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,64; 28,68</t>
+          <t>13,39; 28,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 18,95</t>
+          <t>5,35; 18,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 6,62</t>
+          <t>-3,67; 5,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 11,66</t>
+          <t>-2,42; 11,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 13,04</t>
+          <t>-1,07; 11,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 0,0</t>
+          <t>-7,97; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 19,09</t>
+          <t>8,81; 20,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 14,58</t>
+          <t>4,65; 14,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,46</t>
+          <t>-3,7; 3,52</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>197,65; 1761,99</t>
+          <t>179,67; 1677,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76,55; 1021,12</t>
+          <t>70,1; 991,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,24; 372,46</t>
+          <t>-67,52; 301,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,57; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,34; —</t>
+          <t>-63,88; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>145,86; 1011,2</t>
+          <t>134,81; 1042,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,89; 745,42</t>
+          <t>71,97; 809,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,5; 188,11</t>
+          <t>-76,74; 211,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 7,7</t>
+          <t>-1,85; 7,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -1,72</t>
+          <t>-8,07; -1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; -0,64</t>
+          <t>-7,91; -0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 4,01</t>
+          <t>-2,82; 4,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,18</t>
+          <t>-4,17; 2,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,01</t>
+          <t>-5,51; 0,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,49</t>
+          <t>-1,54; 5,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -0,94</t>
+          <t>-6,3; -0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -1,29</t>
+          <t>-6,33; -0,97</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 197,92</t>
+          <t>-28,31; 200,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -28,18</t>
+          <t>-95,09; -15,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-95,37; 10,27</t>
+          <t>-94,77; 23,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 178,12</t>
+          <t>-23,63; 181,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-93,5; -4,71</t>
+          <t>-93,11; -14,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-94,6; -9,74</t>
+          <t>-93,57; -9,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,2</t>
+          <t>-0,53; 3,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,5</t>
+          <t>-0,18; 4,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 15,22</t>
+          <t>5,69; 14,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,02</t>
+          <t>0,67; 6,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,7</t>
+          <t>-0,2; 2,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,95</t>
+          <t>0,05; 3,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 11,29</t>
+          <t>4,38; 10,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,11</t>
+          <t>-4,58; 3,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 3,32</t>
+          <t>-4,81; 2,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 4,59</t>
+          <t>-4,2; 4,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,76</t>
+          <t>-6,43; 2,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1,75</t>
+          <t>-6,61; 1,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,02</t>
+          <t>-7,81; -0,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,44</t>
+          <t>-4,05; 2,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,84</t>
+          <t>-4,45; 1,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,77</t>
+          <t>-4,41; 1,77</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,18; 167,27</t>
+          <t>-70,99; 159,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,34; 125,66</t>
+          <t>-69,15; 106,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 173,72</t>
+          <t>-66,2; 160,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-67,52; 104,57</t>
+          <t>-69,01; 91,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,57; 64,08</t>
+          <t>-71,23; 59,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,48; 75,77</t>
+          <t>-73,41; 79,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 11,98</t>
+          <t>0,94; 12,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,38</t>
+          <t>-3,52; 5,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 0,0</t>
+          <t>-7,87; -0,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 3,34</t>
+          <t>-13,58; 3,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 0,0</t>
+          <t>-17,3; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 19,09</t>
+          <t>-7,05; 18,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 8,38</t>
+          <t>-1,36; 8,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,59</t>
+          <t>-4,91; 2,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 1,48</t>
+          <t>-5,94; 1,61</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,23; —</t>
+          <t>-11,03; 1285,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 809,96</t>
+          <t>-45,94; 768,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 373,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,81</t>
+          <t>-2,52; 4,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,16</t>
+          <t>-3,25; 3,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,72</t>
+          <t>-0,46; 7,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,2</t>
+          <t>-3,94; 3,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,7</t>
+          <t>-3,46; 3,75</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,34</t>
+          <t>-3,07; 4,05</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,96</t>
+          <t>-2,32; 2,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,39</t>
+          <t>-2,44; 2,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,41</t>
+          <t>-0,54; 5,43</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 553,5</t>
+          <t>-74,02; 628,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-85,46; 390,95</t>
+          <t>-84,14; 369,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 1009,12</t>
+          <t>-31,33; 795,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 262,91</t>
+          <t>-69,51; 325,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-75,02; 279,29</t>
+          <t>-74,07; 252,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 562,4</t>
+          <t>-24,03; 569,96</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 6,01</t>
+          <t>0,57; 6,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,79</t>
+          <t>4,49; 11,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,93; 17,74</t>
+          <t>7,3; 18,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,94</t>
+          <t>0,46; 4,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,79</t>
+          <t>4,49; 11,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,03</t>
+          <t>0,72; 8,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,19</t>
+          <t>0,53; 4,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,3</t>
+          <t>5,1; 9,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,89</t>
+          <t>1,68; 11,4</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 872,69</t>
+          <t>-8,96; 794,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>108,26; 1558,75</t>
+          <t>120,38; 1502,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>179,38; 2306,87</t>
+          <t>178,08; 2543,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,98; 834,49</t>
+          <t>5,89; 817,06</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>181,5; 2061,5</t>
+          <t>172,89; 1831,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>95,05; 1828,63</t>
+          <t>84,88; 1656,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,21</t>
+          <t>0,43; 5,17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,53</t>
+          <t>-0,4; 3,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,0</t>
+          <t>-1,26; 3,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,87</t>
+          <t>-0,61; 3,95</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,85</t>
+          <t>-1,2; 2,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 7,7</t>
+          <t>-0,05; 7,52</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,0</t>
+          <t>0,51; 3,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,67</t>
+          <t>-0,34; 2,8</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,23</t>
+          <t>-0,34; 3,2</t>
         </is>
       </c>
     </row>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 598,92</t>
+          <t>6,92; 598,71</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 426,2</t>
+          <t>-32,01; 430,14</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 312,91</t>
+          <t>-60,93; 383,45</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,48; 476,35</t>
+          <t>7,12; 451,15</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 325,03</t>
+          <t>-24,49; 313,35</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 395,63</t>
+          <t>-26,03; 387,26</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,46</t>
+          <t>2,65; 5,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,94</t>
+          <t>1,17; 3,75</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,06</t>
+          <t>1,94; 5,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,99</t>
+          <t>-0,66; 1,92</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,09</t>
+          <t>0,42; 3,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,34</t>
+          <t>-0,83; 2,34</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,99</t>
+          <t>1,78; 3,88</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,31</t>
+          <t>1,26; 3,22</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,5</t>
+          <t>1,02; 3,55</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>77,48; 238,34</t>
+          <t>77,3; 239,37</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>38,6; 171,03</t>
+          <t>32,65; 166,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>57,58; 217,73</t>
+          <t>60,16; 230,78</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 213,3</t>
+          <t>-36,52; 204,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>17,55; 339,74</t>
+          <t>16,78; 379,73</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 222,15</t>
+          <t>-34,57; 268,77</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>65,46; 205,15</t>
+          <t>61,39; 195,12</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>41,18; 165,44</t>
+          <t>43,92; 168,79</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>38,68; 173,03</t>
+          <t>34,37; 173,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 28,15</t>
+          <t>13,26; 28,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 18,96</t>
+          <t>5,23; 18,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 5,95</t>
+          <t>-4,26; 4,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 11,04</t>
+          <t>-2,81; 12,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 11,97</t>
+          <t>-0,99; 12,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 0,0</t>
+          <t>-9,38; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 20,0</t>
+          <t>8,3; 19,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,52</t>
+          <t>4,97; 14,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,52</t>
+          <t>-3,79; 2,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,56%</t>
+          <t>-25,89%</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>179,67; 1677,77</t>
+          <t>191,5; 1704,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,1; 991,11</t>
+          <t>67,7; 1022,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,52; 301,72</t>
+          <t>-77,53; 289,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,88; —</t>
+          <t>-60,8; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>134,81; 1042,4</t>
+          <t>143,31; 990,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,97; 809,85</t>
+          <t>86,47; 714,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,74; 211,13</t>
+          <t>-76,47; 125,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-4,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-3,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,22</t>
+          <t>-1,48; 7,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -1,32</t>
+          <t>-8,34; -1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; -0,91</t>
+          <t>-8,08; -0,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,52</t>
+          <t>-3,36; 4,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,2</t>
+          <t>-4,13; 2,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,98</t>
+          <t>-5,56; 0,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 5,42</t>
+          <t>-1,07; 5,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; -0,95</t>
+          <t>-6,47; -0,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -0,97</t>
+          <t>-6,16; -0,93</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-71,43%</t>
+          <t>-71,86%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-62,51%</t>
+          <t>-63,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-72,56%</t>
+          <t>-73,18%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 200,0</t>
+          <t>-23,1; 231,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-95,09; -15,81</t>
+          <t>-100,0; -19,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-94,77; 23,27</t>
+          <t>-95,17; 17,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 181,64</t>
+          <t>-20,22; 195,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-93,11; -14,74</t>
+          <t>-93,55; -13,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-93,57; -9,7</t>
+          <t>-94,77; -14,9</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>12,1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>9,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,84</t>
+          <t>-0,67; 3,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,25</t>
+          <t>-0,08; 4,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,87</t>
+          <t>7,55; 17,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,52</t>
+          <t>0,68; 5,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,73</t>
+          <t>-0,14; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,09</t>
+          <t>0,02; 2,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,83</t>
+          <t>5,58; 13,26</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1866,32%</t>
+          <t>2355,26%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2044,71%</t>
+          <t>2541,92%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 3,89</t>
+          <t>-4,19; 4,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,77</t>
+          <t>-4,47; 3,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 4,58</t>
+          <t>-4,43; 4,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,24</t>
+          <t>-5,84; 2,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,71</t>
+          <t>-6,52; 1,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -0,04</t>
+          <t>-7,6; -0,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,34</t>
+          <t>-3,81; 2,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 1,51</t>
+          <t>-4,13; 1,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,77</t>
+          <t>-4,34; 1,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>-9,15%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-79,97%</t>
+          <t>-80,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-29,01%</t>
+          <t>-34,57%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 159,77</t>
+          <t>-65,34; 190,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 106,06</t>
+          <t>-68,66; 140,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 160,58</t>
+          <t>-69,17; 182,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 91,86</t>
+          <t>-69,58; 100,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 59,7</t>
+          <t>-68,05; 77,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 79,68</t>
+          <t>-74,85; 68,89</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 12,55</t>
+          <t>0,42; 12,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,51</t>
+          <t>-3,83; 5,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,86</t>
+          <t>-7,43; -0,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 3,27</t>
+          <t>-13,93; 3,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 0,0</t>
+          <t>-18,53; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 18,8</t>
+          <t>-7,25; 14,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 8,28</t>
+          <t>-1,33; 8,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,59</t>
+          <t>-4,63; 3,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 1,61</t>
+          <t>-5,84; 1,31</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-62,84%</t>
+          <t>-64,99%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 1285,51</t>
+          <t>-16,0; 1348,1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,94; 768,72</t>
+          <t>-44,2; 858,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,78</t>
+          <t>-2,8; 4,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,39</t>
+          <t>-3,28; 3,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 7,94</t>
+          <t>-0,68; 7,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,02</t>
+          <t>-3,64; 2,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,75</t>
+          <t>-3,53; 3,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,05</t>
+          <t>-2,51; 4,82</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,91</t>
+          <t>-2,29; 2,85</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,37</t>
+          <t>-2,49; 2,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,43</t>
+          <t>-0,28; 5,42</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143,54%</t>
+          <t>135,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>112,01%</t>
+          <t>112,38%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-74,02; 628,49</t>
+          <t>-71,92; 822,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,14; 369,73</t>
+          <t>-85,98; 488,38</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 795,79</t>
+          <t>-35,34; 1060,05</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 325,18</t>
+          <t>-70,86; 305,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 252,95</t>
+          <t>-73,36; 232,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 569,96</t>
+          <t>-25,02; 542,49</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>12,36</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>8,66</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>10,71</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,09</t>
+          <t>0,52; 6,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,67</t>
+          <t>4,63; 11,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,3; 18,44</t>
+          <t>8,25; 17,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,2</t>
+          <t>0,46; 4,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,18</t>
+          <t>4,43; 10,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,81</t>
+          <t>5,17; 13,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,53</t>
+          <t>0,47; 4,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,95</t>
+          <t>5,24; 10,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,4</t>
+          <t>7,55; 14,31</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>647,97%</t>
+          <t>680,01%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>538,69%</t>
+          <t>858,23%</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2079,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 794,54</t>
+          <t>-3,87; 813,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>120,38; 1502,12</t>
+          <t>117,67; 1424,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>178,08; 2543,94</t>
+          <t>203,33; 2207,83</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,89; 817,06</t>
+          <t>1,79; 811,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>172,89; 1831,72</t>
+          <t>178,31; 1885,96</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>84,88; 1656,29</t>
+          <t>272,48; 2607,26</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,17</t>
+          <t>0,37; 5,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,59</t>
+          <t>-0,46; 3,67</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,02</t>
+          <t>-1,26; 2,88</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,95</t>
+          <t>-0,76; 3,9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,71</t>
+          <t>-1,21; 2,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,52</t>
+          <t>-0,16; 6,82</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,98</t>
+          <t>0,55; 4,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,8</t>
+          <t>-0,28; 2,7</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,2</t>
+          <t>-0,38; 3,34</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>310,93%</t>
+          <t>297,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -2295,17 +2295,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6,92; 598,71</t>
+          <t>-5,82; 525,99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 430,14</t>
+          <t>-32,72; 370,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 383,45</t>
+          <t>-64,56; 310,99</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,12; 451,15</t>
+          <t>17,44; 534,24</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 313,35</t>
+          <t>-20,19; 365,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 387,26</t>
+          <t>-38,95; 398,64</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,41</t>
+          <t>2,68; 5,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,75</t>
+          <t>1,32; 3,79</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,11</t>
+          <t>2,27; 5,43</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,92</t>
+          <t>-0,57; 2,13</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,12</t>
+          <t>0,45; 3,2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,34</t>
+          <t>0,56; 3,62</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,88</t>
+          <t>1,86; 3,93</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,22</t>
+          <t>1,3; 3,24</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,55</t>
+          <t>2,09; 4,3</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>126,06%</t>
+          <t>137,34%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>133,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>101,1%</t>
+          <t>132,81%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>77,3; 239,37</t>
+          <t>84,0; 248,52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>32,65; 166,84</t>
+          <t>39,89; 173,2</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>60,16; 230,78</t>
+          <t>66,94; 250,37</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 204,3</t>
+          <t>-29,65; 231,32</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>16,78; 379,73</t>
+          <t>16,4; 353,9</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 268,77</t>
+          <t>22,06; 376,64</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>61,39; 195,12</t>
+          <t>65,59; 203,79</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>43,92; 168,79</t>
+          <t>45,83; 165,47</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>34,37; 173,14</t>
+          <t>75,12; 224,5</t>
         </is>
       </c>
     </row>
